--- a/data/yield/South Korea/KOFR.xlsx
+++ b/data/yield/South Korea/KOFR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\yield\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578CD01B-C1F9-4A58-BA1F-74B03E110FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B06B84C-854A-4B56-9308-D236E67085B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOFR" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="11">
   <si>
     <t>KOFR</t>
   </si>
@@ -78,7 +78,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -120,6 +120,12 @@
       <color indexed="8"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -13751,7 +13757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC83E2F-018C-4B5A-96A0-1EEF1FA8E943}">
-  <dimension ref="A1:F2067"/>
+  <dimension ref="A1:F2077"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="8" bestFit="1" customWidth="1"/>
@@ -55100,10 +55106,205 @@
         <v>2.5299999999999998</v>
       </c>
       <c r="F2067" s="11">
+        <v>1188.4208900000001</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2068" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B2068" s="8">
+        <v>46169</v>
+      </c>
+      <c r="C2068" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2068" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2068" s="10">
+        <v>2.54</v>
+      </c>
+      <c r="F2068" s="11">
         <v>1188.7503899999999</v>
       </c>
     </row>
+    <row r="2069" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2069" s="8">
+        <v>46169</v>
+      </c>
+      <c r="B2069" s="8">
+        <v>46170</v>
+      </c>
+      <c r="C2069" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2069" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2069" s="10">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="F2069" s="11">
+        <v>1188.83311</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2070" s="8">
+        <v>46170</v>
+      </c>
+      <c r="B2070" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C2070" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2070" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2070" s="10">
+        <v>2.5379999999999998</v>
+      </c>
+      <c r="F2070" s="11">
+        <v>1188.91617</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2071" s="8">
+        <v>46171</v>
+      </c>
+      <c r="B2071" s="8">
+        <v>46174</v>
+      </c>
+      <c r="C2071" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2071" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2071" s="10">
+        <v>2.56</v>
+      </c>
+      <c r="F2071" s="11">
+        <v>1189.99884</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2072" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B2072" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C2072" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2072" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2072" s="10">
+        <v>2.5390000000000001</v>
+      </c>
+      <c r="F2072" s="11">
+        <v>1189.24902</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2073" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B2073" s="8">
+        <v>46177</v>
+      </c>
+      <c r="C2073" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2073" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2073" s="10">
+        <v>2.5289999999999999</v>
+      </c>
+      <c r="F2073" s="11">
+        <v>1189.3317500000001</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2074" s="8">
+        <v>46177</v>
+      </c>
+      <c r="B2074" s="8">
+        <v>46178</v>
+      </c>
+      <c r="C2074" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2074" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2074" s="10">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="F2074" s="11">
+        <v>1189.49656</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2075" s="8">
+        <v>46178</v>
+      </c>
+      <c r="B2075" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C2075" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2075" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2075" s="10">
+        <v>2.5089999999999999</v>
+      </c>
+      <c r="F2075" s="11">
+        <v>1189.5786499999999</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2076" s="8">
+        <v>46181</v>
+      </c>
+      <c r="B2076" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C2076" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2076" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2076" s="10">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="F2076" s="11">
+        <v>1189.8239599999999</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2077" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B2077" s="8">
+        <v>46183</v>
+      </c>
+      <c r="C2077" s="9">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2077" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
